--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="223">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T12:52:51+00:00</t>
+    <t>2025-02-24T13:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,10 +311,6 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
-</t>
   </si>
   <si>
     <t>EncompassingEncounter.typeId.nullFlavor</t>
@@ -1560,7 +1556,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1568,10 +1564,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1669,39 +1665,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1752,7 +1748,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1772,39 +1768,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1855,7 +1851,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1875,39 +1871,39 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1916,49 +1912,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1978,17 +1974,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -2006,11 +2002,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2061,7 +2057,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2081,10 +2077,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2111,7 +2107,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2162,7 +2158,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2182,10 +2178,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2219,7 +2215,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2241,7 +2237,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2259,7 +2255,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2279,10 +2275,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2316,7 +2312,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2338,7 +2334,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2356,7 +2352,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2376,10 +2372,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2405,7 +2401,7 @@
         <v>95</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2457,7 +2453,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2477,10 +2473,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2503,10 +2499,10 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -2538,7 +2534,7 @@
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2556,7 +2552,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2576,10 +2572,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2677,10 +2673,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2709,7 +2705,7 @@
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2760,7 +2756,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2780,17 +2776,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>75</v>
@@ -2808,11 +2804,11 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2863,7 +2859,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2883,17 +2879,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -2911,11 +2907,11 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2966,7 +2962,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2986,17 +2982,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -3014,11 +3010,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3069,7 +3065,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3089,17 +3085,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>75</v>
@@ -3117,11 +3113,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3172,7 +3168,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3192,10 +3188,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3218,11 +3214,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3273,7 +3269,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3293,10 +3289,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3319,11 +3315,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3374,7 +3370,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3394,39 +3390,39 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="F24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K24" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3477,7 +3473,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3497,39 +3493,39 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="F25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K25" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3580,7 +3576,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3600,17 +3596,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3628,11 +3624,11 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3683,7 +3679,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3703,10 +3699,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3729,10 +3725,10 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -3784,7 +3780,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -3804,10 +3800,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3830,11 +3826,11 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3885,7 +3881,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3905,10 +3901,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3931,10 +3927,10 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -3962,11 +3958,11 @@
         <v>74</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>74</v>
@@ -3984,7 +3980,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4004,10 +4000,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4030,13 +4026,13 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4087,7 +4083,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4107,10 +4103,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4208,10 +4204,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4309,10 +4305,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4402,7 +4398,7 @@
         <v>74</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>74</v>
@@ -4410,10 +4406,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4511,39 +4507,39 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E35" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4594,7 +4590,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4614,39 +4610,39 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E36" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4697,7 +4693,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4717,39 +4713,39 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4758,49 +4754,49 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4820,17 +4816,17 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>75</v>
@@ -4848,11 +4844,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4903,7 +4899,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -4923,10 +4919,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4953,7 +4949,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5004,7 +5000,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5024,10 +5020,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5061,7 +5057,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>74</v>
@@ -5083,7 +5079,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>74</v>
@@ -5101,7 +5097,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5121,10 +5117,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5147,7 +5143,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -5200,7 +5196,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5220,10 +5216,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5246,10 +5242,10 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -5301,7 +5297,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5321,10 +5317,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5347,13 +5343,13 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5404,7 +5400,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5424,10 +5420,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5525,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5626,10 +5622,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5719,7 +5715,7 @@
         <v>74</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>74</v>
@@ -5727,10 +5723,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5828,39 +5824,39 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E48" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K48" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5911,7 +5907,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -5931,39 +5927,39 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K49" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6014,7 +6010,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6034,39 +6030,39 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6075,49 +6071,49 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6137,17 +6133,17 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>75</v>
@@ -6165,11 +6161,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6220,7 +6216,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6240,10 +6236,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6270,7 +6266,7 @@
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6321,7 +6317,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6341,10 +6337,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6378,7 +6374,7 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>74</v>
@@ -6400,7 +6396,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -6418,7 +6414,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6438,10 +6434,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6464,7 +6460,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6517,7 +6513,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:32:36+00:00</t>
+    <t>2025-02-24T13:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:36:50+00:00</t>
+    <t>2025-03-04T16:07:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T13:18:22+00:00</t>
+    <t>2025-03-14T15:47:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>encompassingEncounter</t>
+    <t>CDA - encompassingEncounter</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1005,42 +1005,42 @@
   <dimension ref="A1:AK54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="69.16796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="69.16796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.30078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="59.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="156.125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="133.8515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="92.0703125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="55.87890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="78.93359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="47.90625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-encompassing-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
